--- a/Connectivity Application Data.xlsx
+++ b/Connectivity Application Data.xlsx
@@ -1,30 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\30101554\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\CTU-automated-pdf-extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AFDD15E-72CF-4E3F-B14F-795D2D8BD757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3629EF83-F417-4457-AF63-296181A0774F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{9070875C-CA77-4BB5-B99B-440D4B99D305}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Data Sources" sheetId="6" r:id="rId1"/>
-    <sheet name="Data to be captured" sheetId="1" r:id="rId2"/>
+    <sheet name="Data Sources" sheetId="1" r:id="rId1"/>
+    <sheet name="Data to be captured" sheetId="2" r:id="rId2"/>
     <sheet name="RE Potential" sheetId="3" r:id="rId3"/>
     <sheet name="Margin" sheetId="4" r:id="rId4"/>
-    <sheet name="Transformation Capacity" sheetId="5" r:id="rId5"/>
-    <sheet name="Element Status" sheetId="2" r:id="rId6"/>
+    <sheet name="Non RE proposed RE Integration" sheetId="5" r:id="rId5"/>
+    <sheet name="Transformation Capacity" sheetId="6" r:id="rId6"/>
+    <sheet name="Element Status" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -32,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="207">
   <si>
     <t>SN</t>
   </si>
@@ -156,25 +152,34 @@
     <t>Group</t>
   </si>
   <si>
-    <t>Application ID</t>
+    <t>GNA/ST II Application ID</t>
+  </si>
+  <si>
+    <t>LTA Application ID</t>
   </si>
   <si>
     <t>Application ID under Enhancement 5.2 or revision</t>
   </si>
   <si>
-    <t>CMETS LTA/GNA Approved</t>
-  </si>
-  <si>
-    <t>CMETS LTA/GNA Meeting Date</t>
+    <t>CMETS GNA Approved</t>
+  </si>
+  <si>
+    <t>CMETS LTA Approved</t>
+  </si>
+  <si>
+    <t>CMETS GNA Meeting Date</t>
+  </si>
+  <si>
+    <t>CMETS LTA Meeting Date</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Application Quantum (MW)</t>
-  </si>
-  <si>
-    <t>Status of LTA</t>
+    <t>Application Quantum (MW)(ST II)</t>
+  </si>
+  <si>
+    <t>Granted  Quantum GNA/LTA(MW)</t>
   </si>
   <si>
     <t>Installed/Break-up Capacity (MW)</t>
@@ -189,16 +194,16 @@
     <t>Commissioned</t>
   </si>
   <si>
-    <t>Application Date</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>Applied Start of Connectivity sought by developer</t>
-  </si>
-  <si>
-    <t>GNA Operationalization</t>
+    <t>Application/Submission Date</t>
+  </si>
+  <si>
+    <t>Mode(Criteria for applying)</t>
+  </si>
+  <si>
+    <t>Applied Start of Connectivity sought by developer date( start date of connectivity as per the application)</t>
+  </si>
+  <si>
+    <t>GNA Operationalization Date</t>
   </si>
   <si>
     <t>GNA Operationalization (Yes/No)</t>
@@ -210,6 +215,9 @@
     <t>Nature of Applicant</t>
   </si>
   <si>
+    <t>Status of application(Withdrawn / granted. Revoked.)</t>
+  </si>
+  <si>
     <t>Voltage level</t>
   </si>
   <si>
@@ -297,9 +305,162 @@
     <t xml:space="preserve">Complex </t>
   </si>
   <si>
+    <t>Bikaner</t>
+  </si>
+  <si>
     <t>Data Scoure (Sl. No.(s)9, 10a, )</t>
   </si>
   <si>
+    <t>Kurnool</t>
+  </si>
+  <si>
+    <t>Anantapur</t>
+  </si>
+  <si>
+    <t>Gadag</t>
+  </si>
+  <si>
+    <t>Koppal</t>
+  </si>
+  <si>
+    <t>Rajasthan</t>
+  </si>
+  <si>
+    <t>45 GW   (15 GW Wind &amp; 30  GW solar in GIB  Zone)</t>
+  </si>
+  <si>
+    <t>Andhra Pradesh</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>Tamil Nadu</t>
+  </si>
+  <si>
+    <t>Offshore wind</t>
+  </si>
+  <si>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>Madhya Pradesh</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>5.4</t>
+  </si>
+  <si>
+    <t>8.5</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>Bikaner-II</t>
+  </si>
+  <si>
+    <t>Bikaner-III</t>
+  </si>
+  <si>
+    <t>Fatehgarh-IV</t>
+  </si>
+  <si>
+    <t>Ramgarh</t>
+  </si>
+  <si>
+    <t>Jalore</t>
+  </si>
+  <si>
+    <t>Sanchore</t>
+  </si>
+  <si>
+    <t>Sirohi</t>
+  </si>
+  <si>
+    <t>Pali</t>
+  </si>
+  <si>
+    <t>Ajmer</t>
+  </si>
+  <si>
+    <t>Nagaur</t>
+  </si>
+  <si>
+    <t>Bhadla-IV</t>
+  </si>
+  <si>
+    <t>Barmer-I</t>
+  </si>
+  <si>
+    <t>Barmer-II</t>
+  </si>
+  <si>
+    <t>Jaisalmer/ Jodhpur  (Intra-State)</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Jaisalmer/  Jodhpur   (Intra-State)</t>
+  </si>
+  <si>
+    <t>Jaisalmer/ Jodhpur   (Intra-State)</t>
+  </si>
+  <si>
+    <t>Kurnool-IV</t>
+  </si>
+  <si>
+    <t>Kurnool-V</t>
+  </si>
+  <si>
+    <t>Anantapur-II</t>
+  </si>
+  <si>
+    <t>Kadapa-II</t>
+  </si>
+  <si>
+    <t>Koppal-II</t>
+  </si>
+  <si>
+    <t>Gadag-II</t>
+  </si>
+  <si>
+    <t>Devanagere/  Chitragurga</t>
+  </si>
+  <si>
+    <t>Bijapur</t>
+  </si>
+  <si>
+    <t>Bellary</t>
+  </si>
+  <si>
+    <t>Tumkur-II</t>
+  </si>
+  <si>
+    <t>Nizamabad-II</t>
+  </si>
+  <si>
+    <t>Medak</t>
+  </si>
+  <si>
+    <t>Rangareddy</t>
+  </si>
+  <si>
+    <t>Karimnagar</t>
+  </si>
+  <si>
+    <t>Sl. No.</t>
+  </si>
+  <si>
     <t>Sl.No.</t>
   </si>
   <si>
@@ -357,9 +518,48 @@
     <t>Jul-26 to Dec-31</t>
   </si>
   <si>
+    <t xml:space="preserve">Beyond Dec-25 </t>
+  </si>
+  <si>
     <t>Data Scoure (Sl. No.(s)9)</t>
   </si>
   <si>
+    <t>Name of Station</t>
+  </si>
+  <si>
+    <t>Capacity (MVA)</t>
+  </si>
+  <si>
+    <t>Capacity Allocated (MW)</t>
+  </si>
+  <si>
+    <t>Margin Existing 220kV (MW)</t>
+  </si>
+  <si>
+    <t>Margin Existing 400kV (MW)</t>
+  </si>
+  <si>
+    <t>Line Bays 220kV</t>
+  </si>
+  <si>
+    <t>Line Bays 400kV</t>
+  </si>
+  <si>
+    <t>Margin with ICT 220kV (MW)</t>
+  </si>
+  <si>
+    <t>Margin with ICT 400kV (MW)</t>
+  </si>
+  <si>
+    <t>Line Bays with ICT 220kV</t>
+  </si>
+  <si>
+    <t>Line Bays with ICT 400kV</t>
+  </si>
+  <si>
+    <t>No. of Transformers Required</t>
+  </si>
+  <si>
     <t>S.No.</t>
   </si>
   <si>
@@ -460,13 +660,16 @@
   </si>
   <si>
     <t>Data Scoure (Sl. No.(s)1, 2, 5, 6, 10b, 10c, 10d, 10e, 12)</t>
+  </si>
+  <si>
+    <t>Additional Information of Pooling S/s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -527,6 +730,11 @@
       <name val="Adani Regular"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Adani Regular"/>
     </font>
   </fonts>
   <fills count="6">
@@ -724,10 +932,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -827,15 +1035,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6213563B-77D9-46D0-84DE-7952CE3A773C}"/>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -846,10 +1062,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1168,15 +1380,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45EB2E89-A5F1-4E7E-A87A-CA4707F5CA93}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:D22"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="2" max="2" width="9.140625" style="25"/>
-    <col min="3" max="3" width="116.42578125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" style="25" customWidth="1"/>
+    <col min="3" max="3" width="116.453125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:4" ht="26" customHeight="1">
       <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
@@ -1187,7 +1399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:4">
       <c r="B3" s="23">
         <v>1</v>
       </c>
@@ -1198,7 +1410,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:4" ht="23" customHeight="1">
       <c r="B4" s="23">
         <v>2</v>
       </c>
@@ -1209,7 +1421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:4">
       <c r="B5" s="23">
         <v>3</v>
       </c>
@@ -1220,7 +1432,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:4">
       <c r="B6" s="23">
         <v>4</v>
       </c>
@@ -1231,7 +1443,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:4">
       <c r="B7" s="23">
         <v>5</v>
       </c>
@@ -1242,7 +1454,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:4">
       <c r="B8" s="23">
         <v>6</v>
       </c>
@@ -1253,7 +1465,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:4">
       <c r="B9" s="23">
         <v>7</v>
       </c>
@@ -1264,7 +1476,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:4">
       <c r="B10" s="23">
         <v>8</v>
       </c>
@@ -1275,7 +1487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:4" ht="26" customHeight="1">
       <c r="B12" s="24" t="s">
         <v>0</v>
       </c>
@@ -1286,7 +1498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:4" ht="25" customHeight="1">
       <c r="B13" s="23">
         <v>9</v>
       </c>
@@ -1297,7 +1509,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:4">
       <c r="B14" s="23" t="s">
         <v>15</v>
       </c>
@@ -1308,7 +1520,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="27" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:4" ht="25" customHeight="1">
       <c r="B15" s="23" t="s">
         <v>17</v>
       </c>
@@ -1319,7 +1531,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="2:4" ht="67.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:4" ht="62.5" customHeight="1">
       <c r="B16" s="23" t="s">
         <v>19</v>
       </c>
@@ -1330,7 +1542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="40.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:4" ht="37.5" customHeight="1">
       <c r="B17" s="23" t="s">
         <v>21</v>
       </c>
@@ -1341,7 +1553,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:4">
       <c r="B18" s="23" t="s">
         <v>23</v>
       </c>
@@ -1350,7 +1562,7 @@
       </c>
       <c r="D18" s="14"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:4">
       <c r="B19" s="23">
         <v>11</v>
       </c>
@@ -1361,7 +1573,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:4" ht="25" customHeight="1">
       <c r="B20" s="32">
         <v>12</v>
       </c>
@@ -1372,7 +1584,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:4">
       <c r="B21" s="35">
         <v>13</v>
       </c>
@@ -1383,7 +1595,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:4">
       <c r="B22" s="35">
         <v>14</v>
       </c>
@@ -1396,54 +1608,56 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" xr:uid="{0027BC6C-FE1E-49DE-BCCA-99D9ADE9DB68}"/>
-    <hyperlink ref="C6" r:id="rId2" xr:uid="{36AAC551-4D87-4288-A672-4257E41C3B3F}"/>
-    <hyperlink ref="C7" r:id="rId3" xr:uid="{10322A1F-0D95-4006-8CA9-467CD5AF6708}"/>
-    <hyperlink ref="C8" r:id="rId4" xr:uid="{9576E5CC-956F-43CF-B40F-6BA52417F20A}"/>
-    <hyperlink ref="C9" r:id="rId5" xr:uid="{6CBF7FCF-9BFC-4D7A-AA7D-8BB92E1B03B2}"/>
-    <hyperlink ref="C10" r:id="rId6" xr:uid="{A0D341D1-CCF5-46AB-890E-FD74316B0223}"/>
-    <hyperlink ref="C13" r:id="rId7" xr:uid="{22B76FB3-265D-4AD1-8D3D-F031A96A88DF}"/>
-    <hyperlink ref="C14" r:id="rId8" xr:uid="{7ABEA51F-6C50-48D5-8F80-6F60298350C6}"/>
-    <hyperlink ref="C19" r:id="rId9" xr:uid="{A3C822EC-6EE1-4505-A182-B5958D941D6E}"/>
-    <hyperlink ref="C15" r:id="rId10" display="https://cea.nic.in/comm-trans/national-committee-on-transmission/?lang=en" xr:uid="{3CD1AE45-1CDB-4DD8-AAE5-8654A138A867}"/>
-    <hyperlink ref="C17" r:id="rId11" display="https://cea.nic.in/transmission-reports/?lang=en" xr:uid="{C86739B8-55F2-4802-84E0-5FAF2A516D56}"/>
-    <hyperlink ref="C21" r:id="rId12" display="Global Wind Atlas" xr:uid="{E2B9D915-9F7E-415B-ABB1-08E9D11DDB18}"/>
-    <hyperlink ref="C22" r:id="rId13" location="8.12/23.96/70.256" display="Open Infrastructure Map" xr:uid="{2A29AF61-BEEB-4C2B-A328-439D43B2A623}"/>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C7" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C8" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C10" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C13" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C15" r:id="rId9" display="https://cea.nic.in/comm-trans/national-committee-on-transmission/?lang=en" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C17" r:id="rId10" display="https://cea.nic.in/transmission-reports/?lang=en" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C19" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C21" r:id="rId12" display="Global Wind Atlas" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C22" r:id="rId13" location="8.12/23.96/70.256" display="Open Infrastructure Map" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDCC0D7-2472-4093-B6C3-EA6C7E138F8E}">
-  <dimension ref="A2:AQ9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A2:AU9"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="41.28515625" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="27" max="27" width="15.7109375" customWidth="1"/>
-    <col min="29" max="29" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="16" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16" customWidth="1"/>
-    <col min="34" max="34" width="8" customWidth="1"/>
-    <col min="35" max="35" width="10.42578125" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" customWidth="1"/>
-    <col min="37" max="37" width="13.7109375" customWidth="1"/>
-    <col min="38" max="39" width="11.5703125" customWidth="1"/>
-    <col min="40" max="40" width="10.85546875" hidden="1" customWidth="1"/>
-    <col min="41" max="41" width="0" hidden="1" customWidth="1"/>
-    <col min="42" max="42" width="18.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="41.26953125" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" customWidth="1"/>
+    <col min="6" max="6" width="15.1796875" customWidth="1"/>
+    <col min="9" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="15.1796875" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="10.54296875" customWidth="1"/>
+    <col min="30" max="30" width="15.7265625" customWidth="1"/>
+    <col min="31" max="31" width="11.36328125" customWidth="1"/>
+    <col min="32" max="32" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="16" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="16" customWidth="1"/>
+    <col min="38" max="38" width="8" customWidth="1"/>
+    <col min="39" max="39" width="10.453125" customWidth="1"/>
+    <col min="40" max="40" width="13.54296875" customWidth="1"/>
+    <col min="41" max="41" width="13.7265625" customWidth="1"/>
+    <col min="42" max="43" width="11.54296875" customWidth="1"/>
+    <col min="44" max="44" width="10.81640625" hidden="1" customWidth="1"/>
+    <col min="45" max="45" width="13" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="18.1796875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:43" ht="89.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:47" ht="89.25" customHeight="1">
       <c r="B2" s="7" t="s">
         <v>29</v>
       </c>
@@ -1486,59 +1700,59 @@
       <c r="O2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="18" t="s">
+      <c r="Q2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="T2" s="19"/>
-      <c r="U2" s="20"/>
+      <c r="R2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
       <c r="V2" s="18" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-      <c r="Y2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB2" s="1" t="s">
+      <c r="X2" s="20"/>
+      <c r="Y2" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="AC2" s="1" t="s">
+      <c r="Z2" s="19"/>
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AD2" s="5" t="s">
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AE2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AF2" s="5" t="s">
+      <c r="AF2" s="1" t="s">
         <v>52</v>
       </c>
       <c r="AG2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AH2" s="10" t="s">
+      <c r="AH2" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AI2" s="1" t="s">
+      <c r="AI2" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AJ2" s="1" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AK2" s="1" t="s">
+      <c r="AK2" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="AL2" s="1" t="s">
+      <c r="AL2" s="10" t="s">
         <v>58</v>
       </c>
       <c r="AM2" s="1" t="s">
@@ -1550,14 +1764,26 @@
       <c r="AO2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AP2" s="4" t="s">
+      <c r="AP2" s="1" t="s">
         <v>62</v>
       </c>
       <c r="AQ2" s="1" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="3" spans="1:43" ht="32" x14ac:dyDescent="0.35">
+      <c r="AR2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AT2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU2" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:47" ht="31" customHeight="1">
       <c r="B3" s="8"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1572,57 +1798,61 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
-      <c r="P3" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>66</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="Z3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
+      <c r="Z3" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA3" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>75</v>
+      </c>
       <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
-      <c r="AF3" s="9"/>
+      <c r="AF3" s="2"/>
       <c r="AG3" s="2"/>
       <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
+      <c r="AI3" s="9"/>
       <c r="AJ3" s="2"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
-      <c r="AN3" s="17"/>
+      <c r="AN3" s="2"/>
       <c r="AO3" s="2"/>
+      <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
-    </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="AR3" s="17"/>
+      <c r="AS3" s="2"/>
+      <c r="AU3" s="2"/>
+    </row>
+    <row r="4" spans="1:47">
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -1663,9 +1893,13 @@
       <c r="AM4" s="14"/>
       <c r="AN4" s="14"/>
       <c r="AO4" s="14"/>
+      <c r="AP4" s="14"/>
       <c r="AQ4" s="14"/>
-    </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="AR4" s="14"/>
+      <c r="AS4" s="14"/>
+      <c r="AU4" s="14"/>
+    </row>
+    <row r="5" spans="1:47">
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -1706,9 +1940,13 @@
       <c r="AM5" s="14"/>
       <c r="AN5" s="14"/>
       <c r="AO5" s="14"/>
+      <c r="AP5" s="14"/>
       <c r="AQ5" s="14"/>
-    </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="AR5" s="14"/>
+      <c r="AS5" s="14"/>
+      <c r="AU5" s="14"/>
+    </row>
+    <row r="6" spans="1:47">
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -1749,9 +1987,13 @@
       <c r="AM6" s="14"/>
       <c r="AN6" s="14"/>
       <c r="AO6" s="14"/>
+      <c r="AP6" s="14"/>
       <c r="AQ6" s="14"/>
-    </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="AR6" s="14"/>
+      <c r="AS6" s="14"/>
+      <c r="AU6" s="14"/>
+    </row>
+    <row r="7" spans="1:47">
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -1792,28 +2034,32 @@
       <c r="AM7" s="14"/>
       <c r="AN7" s="14"/>
       <c r="AO7" s="14"/>
+      <c r="AP7" s="14"/>
       <c r="AQ7" s="14"/>
-    </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.35">
+      <c r="AR7" s="14"/>
+      <c r="AS7" s="14"/>
+      <c r="AU7" s="14"/>
+    </row>
+    <row r="9" spans="1:47">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF18F2C-871E-4E6A-8020-CA40AF438235}">
-  <dimension ref="A2:Q4"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A2:Q107"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="39.7109375" customWidth="1"/>
+    <col min="1" max="1" width="39.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="40.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="39" customHeight="1">
       <c r="B2" s="11" t="s">
         <v>30</v>
       </c>
@@ -1821,56 +2067,62 @@
         <v>31</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
+      <c r="D3" s="14" t="s">
+        <v>87</v>
+      </c>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-      <c r="H3" s="14"/>
+      <c r="G3" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="39">
+        <v>1.85</v>
+      </c>
       <c r="I3" s="14"/>
       <c r="J3" s="14"/>
       <c r="K3" s="14"/>
@@ -1881,9 +2133,1748 @@
       <c r="P3" s="14"/>
       <c r="Q3" s="14"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="40">
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="D5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H5" s="40">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="D6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="D7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H7" s="40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="D8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H8" s="40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H9" s="40">
+        <v>15</v>
+      </c>
+      <c r="I9" s="40">
+        <v>1</v>
+      </c>
+      <c r="L9" s="40">
+        <v>60</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="40">
+        <v>18</v>
+      </c>
+      <c r="I10" s="40">
+        <v>2</v>
+      </c>
+      <c r="L10" s="40">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="40">
+        <v>8</v>
+      </c>
+      <c r="I11" s="40">
+        <v>3</v>
+      </c>
+      <c r="L11" s="40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="C12" t="s">
+        <v>97</v>
+      </c>
+      <c r="H12" s="40">
+        <v>5</v>
+      </c>
+      <c r="I12" s="40">
+        <v>4</v>
+      </c>
+      <c r="L12" s="40">
+        <v>5</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="C13" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="40">
+        <v>3</v>
+      </c>
+      <c r="I13" s="40">
+        <v>5</v>
+      </c>
+      <c r="L13" s="40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="C14" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="40">
+        <v>2</v>
+      </c>
+      <c r="I14" s="40">
+        <v>6</v>
+      </c>
+      <c r="L14" s="40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="H15" s="40">
+        <v>5</v>
+      </c>
+      <c r="I15" s="40">
+        <v>7</v>
+      </c>
+      <c r="L15" s="40">
+        <v>5</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="C16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="40">
+        <v>2</v>
+      </c>
+      <c r="I16" s="40">
+        <v>8</v>
+      </c>
+      <c r="L16" s="40">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="17" spans="3:17">
+      <c r="C17" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="40">
+        <v>30</v>
+      </c>
+      <c r="I17" s="40">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17">
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="40">
+        <v>10</v>
+      </c>
+      <c r="I18" s="40">
+        <v>51</v>
+      </c>
+      <c r="L18" s="40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17">
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="40">
+        <v>2</v>
+      </c>
+      <c r="I19" s="40">
+        <v>17</v>
+      </c>
+      <c r="L19" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:17">
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="40">
+        <v>5</v>
+      </c>
+      <c r="I20" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17">
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H21" s="40">
+        <v>1</v>
+      </c>
+      <c r="I21" s="40">
+        <v>13</v>
+      </c>
+      <c r="L21" s="40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17">
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="40">
+        <v>2</v>
+      </c>
+      <c r="I22" s="40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17">
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H23" s="40">
+        <v>5</v>
+      </c>
+      <c r="I23" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17">
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="H24" s="40">
+        <v>1</v>
+      </c>
+      <c r="I24" s="40">
+        <v>7.5</v>
+      </c>
+      <c r="L24" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17">
+      <c r="C25" t="s">
+        <v>93</v>
+      </c>
+      <c r="H25" s="40">
+        <v>60</v>
+      </c>
+      <c r="I25" s="40">
+        <v>15</v>
+      </c>
+      <c r="L25" s="40">
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17">
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17">
+      <c r="C27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17">
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H28" s="40">
+        <v>5.5</v>
+      </c>
+      <c r="I28" s="40">
+        <v>2</v>
+      </c>
+      <c r="L28" s="40">
+        <v>6.5</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17">
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17">
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" s="40">
+        <v>6</v>
+      </c>
+      <c r="I30" s="40">
+        <v>2</v>
+      </c>
+      <c r="L30" s="40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17">
+      <c r="C31" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17">
+      <c r="C32" t="s">
+        <v>95</v>
+      </c>
+      <c r="H32" s="40">
+        <v>33</v>
+      </c>
+      <c r="I32" s="40">
+        <v>18</v>
+      </c>
+      <c r="L32" s="40">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="3:17">
+      <c r="C33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="3:17">
+      <c r="C34" t="s">
+        <v>96</v>
+      </c>
+      <c r="H34" s="40">
+        <v>9</v>
+      </c>
+      <c r="I34" s="40">
+        <v>8</v>
+      </c>
+      <c r="L34" s="40">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="3:17">
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="3:17">
+      <c r="C36" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" s="40">
+        <v>10</v>
+      </c>
+      <c r="I36" s="40">
+        <v>3</v>
+      </c>
+      <c r="L36" s="40">
+        <v>11.5</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="3:17">
+      <c r="C37" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="3:17">
+      <c r="C38" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" t="s">
+        <v>87</v>
+      </c>
+      <c r="G38" t="s">
+        <v>87</v>
+      </c>
+      <c r="H38" s="40">
+        <v>8</v>
+      </c>
+      <c r="I38" s="40">
+        <v>8.1</v>
+      </c>
+      <c r="L38" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="39" spans="3:17">
+      <c r="C39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" t="s">
+        <v>87</v>
+      </c>
+      <c r="H39" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="40" spans="3:17">
+      <c r="C40" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" t="s">
+        <v>87</v>
+      </c>
+      <c r="G40" t="s">
+        <v>87</v>
+      </c>
+      <c r="H40" s="40">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41" spans="3:17">
+      <c r="C41" t="s">
+        <v>99</v>
+      </c>
+      <c r="D41" t="s">
+        <v>87</v>
+      </c>
+      <c r="G41" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="40">
+        <v>9</v>
+      </c>
+      <c r="I41" s="40">
+        <v>8.1</v>
+      </c>
+      <c r="L41" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="42" spans="3:17">
+      <c r="C42" t="s">
+        <v>99</v>
+      </c>
+      <c r="D42" t="s">
+        <v>91</v>
+      </c>
+      <c r="G42" t="s">
+        <v>91</v>
+      </c>
+      <c r="H42" s="40">
+        <v>12</v>
+      </c>
+      <c r="I42" s="40">
+        <v>1000</v>
+      </c>
+      <c r="L42" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="3:17">
+      <c r="C43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43" t="s">
+        <v>91</v>
+      </c>
+      <c r="H43" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="44" spans="3:17">
+      <c r="C44" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" t="s">
+        <v>92</v>
+      </c>
+      <c r="G44" t="s">
+        <v>92</v>
+      </c>
+      <c r="H44" s="40">
+        <v>13</v>
+      </c>
+      <c r="I44" s="40">
+        <v>2500</v>
+      </c>
+      <c r="L44" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="45" spans="3:17">
+      <c r="C45" t="s">
+        <v>99</v>
+      </c>
+      <c r="D45" t="s">
+        <v>92</v>
+      </c>
+      <c r="G45" t="s">
+        <v>92</v>
+      </c>
+      <c r="H45" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="46" spans="3:17">
+      <c r="C46" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" t="s">
+        <v>92</v>
+      </c>
+      <c r="G46" t="s">
+        <v>92</v>
+      </c>
+      <c r="H46" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="3:17">
+      <c r="C47" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" t="s">
+        <v>91</v>
+      </c>
+      <c r="H47" s="40">
+        <v>11</v>
+      </c>
+      <c r="I47" s="40">
+        <v>1500</v>
+      </c>
+      <c r="L47" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48" spans="3:17">
+      <c r="C48" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" t="s">
+        <v>89</v>
+      </c>
+      <c r="G48" t="s">
+        <v>89</v>
+      </c>
+      <c r="H48" s="40">
+        <v>1</v>
+      </c>
+      <c r="I48" s="40">
+        <v>2500</v>
+      </c>
+      <c r="L48" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17">
+      <c r="C49" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" t="s">
+        <v>89</v>
+      </c>
+      <c r="G49" t="s">
+        <v>89</v>
+      </c>
+      <c r="H49" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17">
+      <c r="C50" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" t="s">
+        <v>90</v>
+      </c>
+      <c r="G50" t="s">
+        <v>90</v>
+      </c>
+      <c r="H50" s="40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17">
+      <c r="C51" t="s">
+        <v>99</v>
+      </c>
+      <c r="D51" t="s">
+        <v>89</v>
+      </c>
+      <c r="G51" t="s">
+        <v>89</v>
+      </c>
+      <c r="H51" s="40">
+        <v>3</v>
+      </c>
+      <c r="I51" s="40">
+        <v>3000</v>
+      </c>
+      <c r="L51" s="40">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17">
+      <c r="C52" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52" t="s">
+        <v>89</v>
+      </c>
+      <c r="G52" t="s">
+        <v>89</v>
+      </c>
+      <c r="H52" s="40">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17">
+      <c r="C53" t="s">
+        <v>93</v>
+      </c>
+      <c r="H53" s="40">
+        <v>7</v>
+      </c>
+      <c r="I53" s="40">
+        <v>0</v>
+      </c>
+      <c r="L53" s="40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17">
+      <c r="C54" t="s">
+        <v>93</v>
+      </c>
+      <c r="H54" s="40">
+        <v>6</v>
+      </c>
+      <c r="I54" s="40">
+        <v>6</v>
+      </c>
+      <c r="L54" s="40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17">
+      <c r="C55" t="s">
+        <v>93</v>
+      </c>
+      <c r="H55" s="40">
+        <v>6</v>
+      </c>
+      <c r="I55" s="40">
+        <v>4</v>
+      </c>
+      <c r="L55" s="40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="3:17">
+      <c r="C56" t="s">
+        <v>93</v>
+      </c>
+      <c r="H56" s="40">
+        <v>3</v>
+      </c>
+      <c r="I56" s="40">
+        <v>0</v>
+      </c>
+      <c r="L56" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="3:17">
+      <c r="C57" t="s">
+        <v>93</v>
+      </c>
+      <c r="H57" s="40">
+        <v>2</v>
+      </c>
+      <c r="I57" s="40">
+        <v>0</v>
+      </c>
+      <c r="L57" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17">
+      <c r="C58" t="s">
+        <v>93</v>
+      </c>
+      <c r="H58" s="40">
+        <v>3</v>
+      </c>
+      <c r="I58" s="40">
+        <v>2</v>
+      </c>
+      <c r="L58" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17">
+      <c r="C59" t="s">
+        <v>93</v>
+      </c>
+      <c r="H59" s="40">
+        <v>4</v>
+      </c>
+      <c r="I59" s="40">
+        <v>3</v>
+      </c>
+      <c r="L59" s="40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17">
+      <c r="C60" t="s">
+        <v>93</v>
+      </c>
+      <c r="H60" s="40">
+        <v>6</v>
+      </c>
+      <c r="I60" s="40">
+        <v>0</v>
+      </c>
+      <c r="L60" s="40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17">
+      <c r="C61" t="s">
+        <v>93</v>
+      </c>
+      <c r="H61" s="40">
+        <v>5</v>
+      </c>
+      <c r="I61" s="40">
+        <v>0</v>
+      </c>
+      <c r="L61" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17">
+      <c r="C62" t="s">
+        <v>102</v>
+      </c>
+      <c r="H62" s="40">
+        <v>1</v>
+      </c>
+      <c r="I62" s="40">
+        <v>0</v>
+      </c>
+      <c r="L62" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17">
+      <c r="C63" t="s">
+        <v>102</v>
+      </c>
+      <c r="H63" s="40">
+        <v>1</v>
+      </c>
+      <c r="I63" s="40">
+        <v>1</v>
+      </c>
+      <c r="L63" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17">
+      <c r="C64" t="s">
+        <v>102</v>
+      </c>
+      <c r="H64" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="I64" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="L64" s="40">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="65" spans="3:17">
+      <c r="C65" t="s">
+        <v>101</v>
+      </c>
+      <c r="H65" s="40">
+        <v>5</v>
+      </c>
+      <c r="I65" s="40">
+        <v>5</v>
+      </c>
+      <c r="L65" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="3:17">
+      <c r="C66" t="s">
+        <v>99</v>
+      </c>
+      <c r="H66" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="I66" s="40">
+        <v>1</v>
+      </c>
+      <c r="L66" s="40">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="67" spans="3:17">
+      <c r="C67" t="s">
+        <v>99</v>
+      </c>
+      <c r="H67" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="I67" s="40">
+        <v>0</v>
+      </c>
+      <c r="L67" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="68" spans="3:17">
+      <c r="C68" t="s">
+        <v>96</v>
+      </c>
+      <c r="H68" s="40">
+        <v>2</v>
+      </c>
+      <c r="I68" s="40">
+        <v>2</v>
+      </c>
+      <c r="L68" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="3:17">
+      <c r="C69" t="s">
+        <v>96</v>
+      </c>
+      <c r="H69" s="40">
+        <v>0</v>
+      </c>
+      <c r="I69" s="40">
+        <v>2</v>
+      </c>
+      <c r="L69" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="3:17">
+      <c r="C70" t="s">
+        <v>96</v>
+      </c>
+      <c r="H70" s="40">
+        <v>1.5</v>
+      </c>
+      <c r="I70" s="40">
+        <v>0</v>
+      </c>
+      <c r="L70" s="40">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="71" spans="3:17">
+      <c r="C71" t="s">
+        <v>97</v>
+      </c>
+      <c r="H71" s="40">
+        <v>5</v>
+      </c>
+      <c r="I71" s="40">
+        <v>5</v>
+      </c>
+      <c r="L71" s="40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="3:17">
+      <c r="C72" t="s">
+        <v>97</v>
+      </c>
+      <c r="E72" t="s">
+        <v>107</v>
+      </c>
+      <c r="F72" t="s">
+        <v>107</v>
+      </c>
+      <c r="H72" s="40">
+        <v>7</v>
+      </c>
+      <c r="I72" s="40">
+        <v>0</v>
+      </c>
+      <c r="K72" s="40">
+        <v>0</v>
+      </c>
+      <c r="L72" s="40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="3:17">
+      <c r="C73" t="s">
+        <v>97</v>
+      </c>
+      <c r="E73" t="s">
+        <v>108</v>
+      </c>
+      <c r="F73" t="s">
+        <v>108</v>
+      </c>
+      <c r="H73" s="40">
+        <v>7</v>
+      </c>
+      <c r="I73" s="40">
+        <v>0</v>
+      </c>
+      <c r="K73" s="40">
+        <v>0</v>
+      </c>
+      <c r="L73" s="40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="3:17">
+      <c r="C74" t="s">
+        <v>97</v>
+      </c>
+      <c r="E74" t="s">
+        <v>109</v>
+      </c>
+      <c r="F74" t="s">
+        <v>109</v>
+      </c>
+      <c r="H74" s="40">
+        <v>6</v>
+      </c>
+      <c r="I74" s="40">
+        <v>6</v>
+      </c>
+      <c r="K74" s="40">
+        <v>2</v>
+      </c>
+      <c r="L74" s="40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="3:17">
+      <c r="C75" t="s">
+        <v>97</v>
+      </c>
+      <c r="E75" t="s">
+        <v>110</v>
+      </c>
+      <c r="F75" t="s">
+        <v>110</v>
+      </c>
+      <c r="H75" s="40">
+        <v>6</v>
+      </c>
+      <c r="I75" s="40">
+        <v>4</v>
+      </c>
+      <c r="K75" s="40">
+        <v>2</v>
+      </c>
+      <c r="L75" s="40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="3:17">
+      <c r="C76" t="s">
+        <v>97</v>
+      </c>
+      <c r="E76" t="s">
+        <v>111</v>
+      </c>
+      <c r="F76" t="s">
+        <v>111</v>
+      </c>
+      <c r="H76" s="40">
+        <v>3</v>
+      </c>
+      <c r="I76" s="40">
+        <v>0</v>
+      </c>
+      <c r="K76" s="40">
+        <v>0</v>
+      </c>
+      <c r="L76" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="3:17">
+      <c r="C77" t="s">
+        <v>97</v>
+      </c>
+      <c r="E77" t="s">
+        <v>112</v>
+      </c>
+      <c r="F77" t="s">
+        <v>112</v>
+      </c>
+      <c r="H77" s="40">
+        <v>3</v>
+      </c>
+      <c r="I77" s="40">
+        <v>0</v>
+      </c>
+      <c r="K77" s="40">
+        <v>0</v>
+      </c>
+      <c r="L77" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="3:17">
+      <c r="C78" t="s">
+        <v>97</v>
+      </c>
+      <c r="E78" t="s">
+        <v>113</v>
+      </c>
+      <c r="F78" t="s">
+        <v>113</v>
+      </c>
+      <c r="H78" s="40">
+        <v>3</v>
+      </c>
+      <c r="I78" s="40">
+        <v>0</v>
+      </c>
+      <c r="K78" s="40">
+        <v>0</v>
+      </c>
+      <c r="L78" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="3:17">
+      <c r="C79" t="s">
+        <v>97</v>
+      </c>
+      <c r="E79" t="s">
+        <v>114</v>
+      </c>
+      <c r="F79" t="s">
+        <v>114</v>
+      </c>
+      <c r="H79" s="40">
+        <v>3</v>
+      </c>
+      <c r="I79" s="40">
+        <v>0</v>
+      </c>
+      <c r="K79" s="40">
+        <v>0</v>
+      </c>
+      <c r="L79" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="3:17">
+      <c r="C80" t="s">
+        <v>97</v>
+      </c>
+      <c r="E80" t="s">
+        <v>115</v>
+      </c>
+      <c r="F80" t="s">
+        <v>115</v>
+      </c>
+      <c r="H80" s="40">
+        <v>2</v>
+      </c>
+      <c r="I80" s="40">
+        <v>0</v>
+      </c>
+      <c r="K80" s="40">
+        <v>0</v>
+      </c>
+      <c r="L80" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="3:12">
+      <c r="C81" t="s">
+        <v>97</v>
+      </c>
+      <c r="E81" t="s">
+        <v>116</v>
+      </c>
+      <c r="F81" t="s">
+        <v>116</v>
+      </c>
+      <c r="H81" s="40">
+        <v>2</v>
+      </c>
+      <c r="I81" s="40">
+        <v>0</v>
+      </c>
+      <c r="K81" s="40">
+        <v>0</v>
+      </c>
+      <c r="L81" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="3:12">
+      <c r="C82" t="s">
+        <v>97</v>
+      </c>
+      <c r="E82" t="s">
+        <v>117</v>
+      </c>
+      <c r="F82" t="s">
+        <v>117</v>
+      </c>
+      <c r="H82" s="40">
+        <v>3</v>
+      </c>
+      <c r="I82" s="40">
+        <v>2</v>
+      </c>
+      <c r="K82" s="40">
+        <v>0</v>
+      </c>
+      <c r="L82" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="3:12">
+      <c r="C83" t="s">
+        <v>97</v>
+      </c>
+      <c r="E83" t="s">
+        <v>118</v>
+      </c>
+      <c r="F83" t="s">
+        <v>118</v>
+      </c>
+      <c r="H83" s="40">
+        <v>4</v>
+      </c>
+      <c r="I83" s="40">
+        <v>3</v>
+      </c>
+      <c r="K83" s="40">
+        <v>2</v>
+      </c>
+      <c r="L83" s="40">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="3:12">
+      <c r="C84" t="s">
+        <v>97</v>
+      </c>
+      <c r="E84" t="s">
+        <v>119</v>
+      </c>
+      <c r="F84" t="s">
+        <v>119</v>
+      </c>
+      <c r="H84" s="40">
+        <v>6</v>
+      </c>
+      <c r="I84" s="40">
+        <v>0</v>
+      </c>
+      <c r="K84" s="40">
+        <v>0</v>
+      </c>
+      <c r="L84" s="40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="3:12">
+      <c r="C85" t="s">
+        <v>97</v>
+      </c>
+      <c r="E85" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" t="s">
+        <v>120</v>
+      </c>
+      <c r="H85" s="40">
+        <v>5</v>
+      </c>
+      <c r="I85" s="40">
+        <v>0</v>
+      </c>
+      <c r="K85" s="40">
+        <v>0</v>
+      </c>
+      <c r="L85" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="3:12">
+      <c r="C86" t="s">
+        <v>97</v>
+      </c>
+      <c r="E86" t="s">
+        <v>121</v>
+      </c>
+      <c r="F86" t="s">
+        <v>121</v>
+      </c>
+      <c r="H86" s="40">
+        <v>60</v>
+      </c>
+      <c r="I86" s="40">
+        <v>15</v>
+      </c>
+      <c r="K86" s="40">
+        <v>6</v>
+      </c>
+      <c r="L86" s="40">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87" spans="3:12">
+      <c r="C87" t="s">
+        <v>97</v>
+      </c>
+      <c r="E87" t="s">
+        <v>122</v>
+      </c>
+      <c r="F87" t="s">
+        <v>122</v>
+      </c>
+      <c r="H87" s="40">
+        <v>5</v>
+      </c>
+      <c r="I87" s="40">
+        <v>0</v>
+      </c>
+      <c r="K87" s="40">
+        <v>0</v>
+      </c>
+      <c r="L87" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="3:12">
+      <c r="C88" t="s">
+        <v>97</v>
+      </c>
+      <c r="E88" t="s">
+        <v>123</v>
+      </c>
+      <c r="F88" t="s">
+        <v>123</v>
+      </c>
+      <c r="H88" s="40">
+        <v>5</v>
+      </c>
+      <c r="I88" s="40">
+        <v>0</v>
+      </c>
+      <c r="K88" s="40">
+        <v>0</v>
+      </c>
+      <c r="L88" s="40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="3:12">
+      <c r="C89" t="s">
+        <v>97</v>
+      </c>
+      <c r="E89" t="s">
+        <v>124</v>
+      </c>
+      <c r="F89" t="s">
+        <v>124</v>
+      </c>
+      <c r="H89" s="40">
+        <v>7.5</v>
+      </c>
+      <c r="I89" s="40">
+        <v>4</v>
+      </c>
+      <c r="K89" s="40">
+        <v>3</v>
+      </c>
+      <c r="L89" s="40">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="90" spans="3:12">
+      <c r="C90" t="s">
+        <v>97</v>
+      </c>
+      <c r="E90" t="s">
+        <v>125</v>
+      </c>
+      <c r="F90" t="s">
+        <v>125</v>
+      </c>
+      <c r="H90" s="40">
+        <v>7.5</v>
+      </c>
+      <c r="I90" s="40">
+        <v>4</v>
+      </c>
+      <c r="K90" s="40">
+        <v>3</v>
+      </c>
+      <c r="L90" s="40">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="91" spans="3:12">
+      <c r="C91" t="s">
+        <v>97</v>
+      </c>
+      <c r="E91" t="s">
+        <v>90</v>
+      </c>
+      <c r="F91" t="s">
+        <v>90</v>
+      </c>
+      <c r="H91" s="40">
+        <v>2</v>
+      </c>
+      <c r="I91" s="40">
+        <v>2</v>
+      </c>
+      <c r="K91" s="40">
+        <v>1</v>
+      </c>
+      <c r="L91" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:12">
+      <c r="C92" t="s">
+        <v>97</v>
+      </c>
+      <c r="E92" t="s">
+        <v>126</v>
+      </c>
+      <c r="F92" t="s">
+        <v>126</v>
+      </c>
+      <c r="H92" s="40">
+        <v>8</v>
+      </c>
+      <c r="I92" s="40">
+        <v>8</v>
+      </c>
+      <c r="K92" s="40">
+        <v>4</v>
+      </c>
+      <c r="L92" s="40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" spans="3:12">
+      <c r="C93" t="s">
+        <v>97</v>
+      </c>
+      <c r="E93" t="s">
+        <v>127</v>
+      </c>
+      <c r="F93" t="s">
+        <v>127</v>
+      </c>
+      <c r="H93" s="40">
+        <v>8</v>
+      </c>
+      <c r="I93" s="40">
+        <v>0</v>
+      </c>
+      <c r="K93" s="40">
+        <v>3</v>
+      </c>
+      <c r="L93" s="40">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="3:12">
+      <c r="C94" t="s">
+        <v>97</v>
+      </c>
+      <c r="E94" t="s">
+        <v>121</v>
+      </c>
+      <c r="F94" t="s">
+        <v>121</v>
+      </c>
+      <c r="H94" s="40">
+        <v>33</v>
+      </c>
+      <c r="I94" s="40">
+        <v>18</v>
+      </c>
+      <c r="K94" s="40">
+        <v>14</v>
+      </c>
+      <c r="L94" s="40">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="95" spans="3:12">
+      <c r="C95" t="s">
+        <v>97</v>
+      </c>
+      <c r="E95" t="s">
+        <v>128</v>
+      </c>
+      <c r="F95" t="s">
+        <v>128</v>
+      </c>
+      <c r="H95" s="40">
+        <v>2</v>
+      </c>
+      <c r="I95" s="40">
+        <v>2</v>
+      </c>
+      <c r="K95" s="40">
+        <v>1</v>
+      </c>
+      <c r="L95" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="3:12">
+      <c r="C96" t="s">
+        <v>97</v>
+      </c>
+      <c r="E96" t="s">
+        <v>129</v>
+      </c>
+      <c r="F96" t="s">
+        <v>129</v>
+      </c>
+      <c r="H96" s="40">
+        <v>2</v>
+      </c>
+      <c r="I96" s="40">
+        <v>2</v>
+      </c>
+      <c r="K96" s="40">
+        <v>1</v>
+      </c>
+      <c r="L96" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:12">
+      <c r="C97" t="s">
+        <v>97</v>
+      </c>
+      <c r="E97" t="s">
+        <v>130</v>
+      </c>
+      <c r="F97" t="s">
+        <v>130</v>
+      </c>
+      <c r="H97" s="40">
+        <v>2</v>
+      </c>
+      <c r="I97" s="40">
+        <v>2</v>
+      </c>
+      <c r="K97" s="40">
+        <v>1</v>
+      </c>
+      <c r="L97" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="3:12">
+      <c r="C98" t="s">
+        <v>97</v>
+      </c>
+      <c r="E98" t="s">
+        <v>131</v>
+      </c>
+      <c r="F98" t="s">
+        <v>131</v>
+      </c>
+      <c r="H98" s="40">
+        <v>0</v>
+      </c>
+      <c r="I98" s="40">
+        <v>2</v>
+      </c>
+      <c r="K98" s="40">
+        <v>0</v>
+      </c>
+      <c r="L98" s="40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="3:12">
+      <c r="C99" t="s">
+        <v>97</v>
+      </c>
+      <c r="E99" t="s">
+        <v>132</v>
+      </c>
+      <c r="F99" t="s">
+        <v>132</v>
+      </c>
+      <c r="H99" s="40">
+        <v>1.5</v>
+      </c>
+      <c r="I99" s="40">
+        <v>0</v>
+      </c>
+      <c r="K99" s="40">
+        <v>0</v>
+      </c>
+      <c r="L99" s="40">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="100" spans="3:12">
+      <c r="C100" t="s">
+        <v>97</v>
+      </c>
+      <c r="E100" t="s">
+        <v>133</v>
+      </c>
+      <c r="F100" t="s">
+        <v>133</v>
+      </c>
+      <c r="H100" s="40">
+        <v>1.5</v>
+      </c>
+      <c r="I100" s="40">
+        <v>0</v>
+      </c>
+      <c r="K100" s="40">
+        <v>0</v>
+      </c>
+      <c r="L100" s="40">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="101" spans="3:12">
+      <c r="C101" t="s">
+        <v>97</v>
+      </c>
+      <c r="E101" t="s">
+        <v>121</v>
+      </c>
+      <c r="F101" t="s">
+        <v>121</v>
+      </c>
+      <c r="H101" s="40">
+        <v>9</v>
+      </c>
+      <c r="I101" s="40">
+        <v>8</v>
+      </c>
+      <c r="K101" s="40">
+        <v>3</v>
+      </c>
+      <c r="L101" s="40">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="102" spans="3:12">
+      <c r="C102" t="s">
+        <v>97</v>
+      </c>
+      <c r="E102" t="s">
+        <v>134</v>
+      </c>
+      <c r="F102" t="s">
+        <v>134</v>
+      </c>
+      <c r="H102" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="I102" s="40">
+        <v>1</v>
+      </c>
+      <c r="K102" s="40">
+        <v>1</v>
+      </c>
+      <c r="L102" s="40">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="103" spans="3:12">
+      <c r="C103" t="s">
+        <v>97</v>
+      </c>
+      <c r="E103" t="s">
+        <v>135</v>
+      </c>
+      <c r="F103" t="s">
+        <v>135</v>
+      </c>
+      <c r="H103" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="I103" s="40">
+        <v>1</v>
+      </c>
+      <c r="K103" s="40">
+        <v>1</v>
+      </c>
+      <c r="L103" s="40">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="104" spans="3:12">
+      <c r="C104" t="s">
+        <v>97</v>
+      </c>
+      <c r="E104" t="s">
+        <v>136</v>
+      </c>
+      <c r="F104" t="s">
+        <v>136</v>
+      </c>
+      <c r="H104" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="I104" s="40">
+        <v>1</v>
+      </c>
+      <c r="K104" s="40">
+        <v>1</v>
+      </c>
+      <c r="L104" s="40">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="105" spans="3:12">
+      <c r="C105" t="s">
+        <v>97</v>
+      </c>
+      <c r="E105" t="s">
+        <v>137</v>
+      </c>
+      <c r="F105" t="s">
+        <v>137</v>
+      </c>
+      <c r="H105" s="40">
+        <v>2.5</v>
+      </c>
+      <c r="I105" s="40">
+        <v>0</v>
+      </c>
+      <c r="K105" s="40">
+        <v>0</v>
+      </c>
+      <c r="L105" s="40">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="106" spans="3:12">
+      <c r="C106" t="s">
+        <v>97</v>
+      </c>
+      <c r="E106" t="s">
+        <v>121</v>
+      </c>
+      <c r="F106" t="s">
+        <v>121</v>
+      </c>
+      <c r="H106" s="40">
+        <v>10</v>
+      </c>
+      <c r="I106" s="40">
+        <v>3</v>
+      </c>
+      <c r="K106" s="40">
+        <v>3</v>
+      </c>
+      <c r="L106" s="40">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="3:12">
+      <c r="C107" t="s">
+        <v>97</v>
+      </c>
+      <c r="E107" t="s">
+        <v>138</v>
+      </c>
+      <c r="F107" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1892,23 +3883,25 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D8C197E-9C6C-4677-A5F0-2524ABF20077}">
-  <dimension ref="A2:W9"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A2:X9"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="39.85546875" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5703125" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" customWidth="1"/>
-    <col min="9" max="9" width="33" customWidth="1"/>
-    <col min="10" max="10" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="23" max="23" width="60.140625" customWidth="1"/>
+    <col min="1" max="1" width="39.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="20.90625" customWidth="1"/>
+    <col min="8" max="8" width="19.54296875" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" customWidth="1"/>
+    <col min="10" max="10" width="33" customWidth="1"/>
+    <col min="11" max="11" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="24" max="24" width="60.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:23" ht="64" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24" ht="62" customHeight="1">
       <c r="B2" s="7" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>31</v>
@@ -1917,106 +3910,110 @@
         <v>30</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="H2" s="4"/>
+        <v>206</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="I2" s="4"/>
-      <c r="J2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="L2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="M2" s="4"/>
-      <c r="N2" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="O2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="P2" s="4"/>
-      <c r="Q2" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="R2" s="4"/>
+      <c r="Q2" s="4"/>
+      <c r="R2" s="4" t="s">
+        <v>145</v>
+      </c>
       <c r="S2" s="4"/>
-      <c r="T2" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="U2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="V2" s="4"/>
-      <c r="W2" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" ht="32" x14ac:dyDescent="0.35">
+      <c r="W2" s="4"/>
+      <c r="X2" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="31" customHeight="1">
       <c r="B3" s="8"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="6" t="s">
-        <v>93</v>
-      </c>
+      <c r="G3" s="2"/>
       <c r="H3" s="6" t="s">
-        <v>94</v>
+        <v>148</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K3" s="2"/>
       <c r="L3" s="6" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="N3" s="6" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="W3" s="6"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+      <c r="W3" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="X3" s="6"/>
+    </row>
+    <row r="4" spans="1:24">
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
       <c r="E4" s="14"/>
-      <c r="F4" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="G4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="26" t="s">
+        <v>154</v>
+      </c>
       <c r="H4" s="14"/>
       <c r="I4" s="14"/>
       <c r="J4" s="14"/>
@@ -2033,16 +4030,17 @@
       <c r="U4" s="14"/>
       <c r="V4" s="14"/>
       <c r="W4" s="14"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X4" s="14"/>
+    </row>
+    <row r="5" spans="1:24">
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
       <c r="E5" s="14"/>
-      <c r="F5" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14" t="s">
+        <v>155</v>
+      </c>
       <c r="H5" s="14"/>
       <c r="I5" s="14"/>
       <c r="J5" s="14"/>
@@ -2059,16 +4057,17 @@
       <c r="U5" s="14"/>
       <c r="V5" s="14"/>
       <c r="W5" s="14"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X5" s="14"/>
+    </row>
+    <row r="6" spans="1:24">
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
       <c r="E6" s="14"/>
-      <c r="F6" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="G6" s="14"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14" t="s">
+        <v>156</v>
+      </c>
       <c r="H6" s="14"/>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
@@ -2085,16 +4084,17 @@
       <c r="U6" s="14"/>
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X6" s="14"/>
+    </row>
+    <row r="7" spans="1:24">
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
       <c r="E7" s="14"/>
-      <c r="F7" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="G7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14" t="s">
+        <v>157</v>
+      </c>
       <c r="H7" s="14"/>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
@@ -2111,30 +4111,112 @@
       <c r="U7" s="14"/>
       <c r="V7" s="14"/>
       <c r="W7" s="14"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="X7" s="14"/>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
+      <c r="L8" s="14"/>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14"/>
+      <c r="P8" s="14"/>
+      <c r="Q8" s="14"/>
+      <c r="R8" s="14"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="14"/>
+      <c r="U8" s="14"/>
+      <c r="V8" s="14"/>
+      <c r="W8" s="14"/>
+      <c r="X8" s="14"/>
+    </row>
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC95502C-EF58-4807-8A73-393318583D69}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="B4:O4"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetData>
+    <row r="4" spans="2:15" ht="52">
+      <c r="B4" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="F4" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="J4" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="L4" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="M4" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="N4" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="O4" s="38" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A3:H6"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="39.28515625" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="B3" s="13" t="s">
-        <v>104</v>
+        <v>172</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>30</v>
@@ -2146,16 +4228,16 @@
         <v>32</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>106</v>
+        <v>174</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -2164,9 +4246,9 @@
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2174,71 +4256,72 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A92DA2CE-E5BA-47FB-ADE6-218C51B1146D}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:AD6"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" customWidth="1"/>
-    <col min="5" max="16" width="15.42578125" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" customWidth="1"/>
-    <col min="26" max="26" width="10.42578125" customWidth="1"/>
+    <col min="1" max="1" width="37.81640625" customWidth="1"/>
+    <col min="2" max="2" width="20.54296875" customWidth="1"/>
+    <col min="3" max="3" width="21.26953125" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" customWidth="1"/>
+    <col min="5" max="16" width="15.453125" customWidth="1"/>
+    <col min="22" max="22" width="11.1796875" customWidth="1"/>
+    <col min="26" max="26" width="10.453125" customWidth="1"/>
     <col min="27" max="27" width="10" customWidth="1"/>
-    <col min="28" max="28" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.7265625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="16" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:30" ht="48" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:30" ht="46.5" customHeight="1">
       <c r="B2" s="1" t="s">
-        <v>108</v>
+        <v>176</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>114</v>
+        <v>182</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>115</v>
+        <v>183</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>118</v>
+        <v>186</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>122</v>
+        <v>190</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
@@ -2248,21 +4331,21 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4" t="s">
-        <v>123</v>
+        <v>191</v>
       </c>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4" t="s">
-        <v>124</v>
+        <v>192</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="AD2" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30" ht="48" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" ht="62" customHeight="1">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2279,43 +4362,43 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="6" t="s">
-        <v>126</v>
+        <v>194</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>128</v>
+        <v>196</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>131</v>
+        <v>199</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>133</v>
+        <v>201</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>134</v>
+        <v>202</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
       <c r="AD3" s="2"/>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30">
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -2332,7 +4415,7 @@
       </c>
       <c r="N4" s="15">
         <f ca="1">DATE(YEAR(TODAY()), MONTH(TODAY()+M4), DAY(TODAY()))</f>
-        <v>45928</v>
+        <v>45667</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
@@ -2360,7 +4443,7 @@
       <c r="AC4" s="14"/>
       <c r="AD4" s="14"/>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30">
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -2373,14 +4456,14 @@
       <c r="K5" s="14"/>
       <c r="L5" s="15">
         <f ca="1">TODAY()</f>
-        <v>45897</v>
+        <v>46001</v>
       </c>
       <c r="M5" s="14">
         <v>21</v>
       </c>
       <c r="N5" s="15">
         <f ca="1">DATE(YEAR(L5),MONTH(L5)+M5,DAY(L5))</f>
-        <v>46535</v>
+        <v>46640</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
@@ -2399,13 +4482,13 @@
       <c r="AC5" s="14"/>
       <c r="AD5" s="14"/>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>137</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
--- a/Connectivity Application Data.xlsx
+++ b/Connectivity Application Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\CTU-automated-pdf-extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3629EF83-F417-4457-AF63-296181A0774F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ED40F2-567E-41DC-B8A3-B3EB89C23B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sources" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="208">
   <si>
     <t>SN</t>
   </si>
@@ -563,15 +563,6 @@
     <t>S.No.</t>
   </si>
   <si>
-    <t xml:space="preserve">Existing </t>
-  </si>
-  <si>
-    <t>Under Implementation</t>
-  </si>
-  <si>
-    <t>Planned</t>
-  </si>
-  <si>
     <t>Element Code</t>
   </si>
   <si>
@@ -663,6 +654,18 @@
   </si>
   <si>
     <t>Additional Information of Pooling S/s</t>
+  </si>
+  <si>
+    <t>Voltage level (kV)</t>
+  </si>
+  <si>
+    <t>Existing Capacity (MVA)</t>
+  </si>
+  <si>
+    <t>Under Implementation Capacity (MVA)</t>
+  </si>
+  <si>
+    <t>Planned Capacity (MVA)</t>
   </si>
 </sst>
 </file>
@@ -935,7 +938,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1043,6 +1046,9 @@
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -3913,7 +3919,7 @@
         <v>140</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>141</v>
@@ -4207,14 +4213,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A3:H6"/>
+  <dimension ref="A3:I6"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="39.26953125" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="4" max="4" width="13.90625" customWidth="1"/>
+    <col min="5" max="6" width="19.453125" customWidth="1"/>
+    <col min="7" max="7" width="17.90625" customWidth="1"/>
+    <col min="8" max="8" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9" ht="37.5">
       <c r="B3" s="13" t="s">
         <v>172</v>
       </c>
@@ -4228,16 +4240,19 @@
         <v>32</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>204</v>
+      </c>
+      <c r="G3" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="H3" s="41" t="s">
+        <v>206</v>
+      </c>
+      <c r="I3" s="41" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
       <c r="D4" s="14"/>
@@ -4245,8 +4260,9 @@
       <c r="F4" s="14"/>
       <c r="G4" s="14"/>
       <c r="H4" s="14"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I4" s="14"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>159</v>
       </c>
@@ -4276,52 +4292,52 @@
   <sheetData>
     <row r="2" spans="1:30" ht="46.5" customHeight="1">
       <c r="B2" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>85</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="Q2" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>190</v>
       </c>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
@@ -4331,15 +4347,15 @@
       <c r="W2" s="4"/>
       <c r="X2" s="4"/>
       <c r="Y2" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AD2" s="4" t="s">
         <v>67</v>
@@ -4362,37 +4378,37 @@
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
       <c r="Q3" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="R3" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="S3" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="T3" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="U3" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="V3" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="W3" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="X3" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="Y3" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="AA3" s="6" t="s">
         <v>201</v>
-      </c>
-      <c r="Y3" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z3" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="AA3" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="AB3" s="2"/>
       <c r="AC3" s="2"/>
@@ -4415,7 +4431,7 @@
       </c>
       <c r="N4" s="15">
         <f ca="1">DATE(YEAR(TODAY()), MONTH(TODAY()+M4), DAY(TODAY()))</f>
-        <v>45667</v>
+        <v>45679</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
@@ -4456,14 +4472,14 @@
       <c r="K5" s="14"/>
       <c r="L5" s="15">
         <f ca="1">TODAY()</f>
-        <v>46001</v>
+        <v>46013</v>
       </c>
       <c r="M5" s="14">
         <v>21</v>
       </c>
       <c r="N5" s="15">
         <f ca="1">DATE(YEAR(L5),MONTH(L5)+M5,DAY(L5))</f>
-        <v>46640</v>
+        <v>46652</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
@@ -4484,7 +4500,7 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>

--- a/Connectivity Application Data.xlsx
+++ b/Connectivity Application Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\CTU-automated-pdf-extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76ED40F2-567E-41DC-B8A3-B3EB89C23B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93662958-8F8F-4955-B491-D508AF8F2483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sources" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="215">
   <si>
     <t>SN</t>
   </si>
@@ -666,6 +666,27 @@
   </si>
   <si>
     <t>Planned Capacity (MVA)</t>
+  </si>
+  <si>
+    <t>JCC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.09.2025 </t>
+  </si>
+  <si>
+    <t>Solar + BESS</t>
+  </si>
+  <si>
+    <t>300 +240</t>
+  </si>
+  <si>
+    <t>Generating station(s), including REGS(s), without ESS</t>
+  </si>
+  <si>
+    <t>Cmets , JCC</t>
+  </si>
+  <si>
+    <t>CMETS</t>
   </si>
 </sst>
 </file>
@@ -1634,7 +1655,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:AU9"/>
+  <dimension ref="A1:AU9"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="41.26953125" customWidth="1"/>
@@ -1644,6 +1665,7 @@
     <col min="11" max="11" width="24.54296875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.1796875" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="15.1796875" customWidth="1"/>
+    <col min="16" max="16" width="13.54296875" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
     <col min="18" max="18" width="10.54296875" customWidth="1"/>
     <col min="30" max="30" width="15.7265625" customWidth="1"/>
@@ -1663,6 +1685,81 @@
     <col min="46" max="46" width="18.1796875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:47" ht="50">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14">
+        <v>1200002471</v>
+      </c>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14">
+        <v>2200002280</v>
+      </c>
+      <c r="L1" s="14">
+        <v>40</v>
+      </c>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q1" s="14">
+        <v>300</v>
+      </c>
+      <c r="R1" s="14">
+        <v>300</v>
+      </c>
+      <c r="S1" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14">
+        <v>300</v>
+      </c>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="AC1" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+      <c r="AH1" s="14"/>
+      <c r="AI1" s="14"/>
+      <c r="AJ1" s="26" t="s">
+        <v>212</v>
+      </c>
+      <c r="AK1" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="AL1" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="AM1" s="14"/>
+      <c r="AN1" s="14"/>
+      <c r="AO1" s="14"/>
+      <c r="AP1" s="14"/>
+      <c r="AQ1" s="14"/>
+      <c r="AR1" s="14"/>
+      <c r="AS1" s="14"/>
+      <c r="AU1" s="14"/>
+    </row>
     <row r="2" spans="1:47" ht="89.25" customHeight="1">
       <c r="B2" s="7" t="s">
         <v>29</v>
@@ -1857,53 +1954,6 @@
       <c r="AR3" s="17"/>
       <c r="AS3" s="2"/>
       <c r="AU3" s="2"/>
-    </row>
-    <row r="4" spans="1:47">
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14"/>
-      <c r="S4" s="14"/>
-      <c r="T4" s="14"/>
-      <c r="U4" s="14"/>
-      <c r="V4" s="14"/>
-      <c r="W4" s="14"/>
-      <c r="X4" s="14"/>
-      <c r="Y4" s="14"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="14"/>
-      <c r="AG4" s="14"/>
-      <c r="AH4" s="14"/>
-      <c r="AI4" s="14"/>
-      <c r="AJ4" s="14"/>
-      <c r="AK4" s="14"/>
-      <c r="AL4" s="14"/>
-      <c r="AM4" s="14"/>
-      <c r="AN4" s="14"/>
-      <c r="AO4" s="14"/>
-      <c r="AP4" s="14"/>
-      <c r="AQ4" s="14"/>
-      <c r="AR4" s="14"/>
-      <c r="AS4" s="14"/>
-      <c r="AU4" s="14"/>
     </row>
     <row r="5" spans="1:47">
       <c r="B5" s="14"/>
@@ -1933,7 +1983,9 @@
       <c r="Z5" s="14"/>
       <c r="AA5" s="14"/>
       <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
+      <c r="AC5" s="14">
+        <v>996</v>
+      </c>
       <c r="AD5" s="14"/>
       <c r="AE5" s="14"/>
       <c r="AF5" s="14"/>
@@ -4431,7 +4483,7 @@
       </c>
       <c r="N4" s="15">
         <f ca="1">DATE(YEAR(TODAY()), MONTH(TODAY()+M4), DAY(TODAY()))</f>
-        <v>45679</v>
+        <v>46068</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
@@ -4472,14 +4524,14 @@
       <c r="K5" s="14"/>
       <c r="L5" s="15">
         <f ca="1">TODAY()</f>
-        <v>46013</v>
+        <v>46037</v>
       </c>
       <c r="M5" s="14">
         <v>21</v>
       </c>
       <c r="N5" s="15">
         <f ca="1">DATE(YEAR(L5),MONTH(L5)+M5,DAY(L5))</f>
-        <v>46652</v>
+        <v>46675</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>

--- a/Connectivity Application Data.xlsx
+++ b/Connectivity Application Data.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\CTU-automated-pdf-extraction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93662958-8F8F-4955-B491-D508AF8F2483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E14165F-19D5-4C36-9A08-5F886AD5D019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="3" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Sources" sheetId="1" r:id="rId1"/>
     <sheet name="Data to be captured" sheetId="2" r:id="rId2"/>
-    <sheet name="RE Potential" sheetId="3" r:id="rId3"/>
-    <sheet name="Margin" sheetId="4" r:id="rId4"/>
-    <sheet name="Non RE proposed RE Integration" sheetId="5" r:id="rId5"/>
-    <sheet name="Transformation Capacity" sheetId="6" r:id="rId6"/>
-    <sheet name="Element Status" sheetId="7" r:id="rId7"/>
+    <sheet name="Bulk Consumers" sheetId="8" r:id="rId3"/>
+    <sheet name="RE Potential" sheetId="3" r:id="rId4"/>
+    <sheet name="Margin" sheetId="4" r:id="rId5"/>
+    <sheet name="Non RE proposed RE Integration" sheetId="5" r:id="rId6"/>
+    <sheet name="Transformation Capacity" sheetId="6" r:id="rId7"/>
+    <sheet name="Element Status" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="226">
   <si>
     <t>SN</t>
   </si>
@@ -687,13 +688,46 @@
   </si>
   <si>
     <t>CMETS</t>
+  </si>
+  <si>
+    <t>Connectivity Under Process</t>
+  </si>
+  <si>
+    <t>Hydro</t>
+  </si>
+  <si>
+    <t>GNA Application ID</t>
+  </si>
+  <si>
+    <t>GNA Type</t>
+  </si>
+  <si>
+    <t>Quantum (MW)</t>
+  </si>
+  <si>
+    <t>Within Region</t>
+  </si>
+  <si>
+    <t>Outside Region</t>
+  </si>
+  <si>
+    <t>Total Quantum (MW)</t>
+  </si>
+  <si>
+    <t>Status of application (Applied/Withdrawn / Granted. Revoked.)</t>
+  </si>
+  <si>
+    <t>Start Date of GNA</t>
+  </si>
+  <si>
+    <t>End Date of GNA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -760,8 +794,27 @@
       <sz val="10"/>
       <name val="Adani Regular"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Adani Regular"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Adani Regular"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Adani Regular"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -792,8 +845,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCAEDFB"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -953,13 +1012,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1069,6 +1148,34 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1655,7 +1762,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AU9"/>
+  <dimension ref="A1:AV9"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="41.26953125" customWidth="1"/>
@@ -1668,24 +1775,24 @@
     <col min="16" max="16" width="13.54296875" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
     <col min="18" max="18" width="10.54296875" customWidth="1"/>
-    <col min="30" max="30" width="15.7265625" customWidth="1"/>
-    <col min="31" max="31" width="11.36328125" customWidth="1"/>
-    <col min="32" max="32" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="20.26953125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="23.26953125" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="16" customWidth="1"/>
-    <col min="38" max="38" width="8" customWidth="1"/>
-    <col min="39" max="39" width="10.453125" customWidth="1"/>
-    <col min="40" max="40" width="13.54296875" customWidth="1"/>
-    <col min="41" max="41" width="13.7265625" customWidth="1"/>
-    <col min="42" max="43" width="11.54296875" customWidth="1"/>
-    <col min="44" max="44" width="10.81640625" hidden="1" customWidth="1"/>
-    <col min="45" max="45" width="13" hidden="1" customWidth="1"/>
-    <col min="46" max="46" width="18.1796875" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="15.7265625" customWidth="1"/>
+    <col min="32" max="32" width="11.36328125" customWidth="1"/>
+    <col min="33" max="33" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="16" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="23.26953125" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="16" customWidth="1"/>
+    <col min="39" max="39" width="8" customWidth="1"/>
+    <col min="40" max="40" width="10.453125" customWidth="1"/>
+    <col min="41" max="41" width="13.54296875" customWidth="1"/>
+    <col min="42" max="42" width="13.7265625" customWidth="1"/>
+    <col min="43" max="44" width="11.54296875" customWidth="1"/>
+    <col min="45" max="45" width="10.81640625" hidden="1" customWidth="1"/>
+    <col min="46" max="46" width="13" hidden="1" customWidth="1"/>
+    <col min="47" max="47" width="18.1796875" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="50">
+    <row r="1" spans="1:48" ht="50">
       <c r="B1" s="14"/>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -1723,44 +1830,45 @@
       <c r="T1" s="14"/>
       <c r="U1" s="14"/>
       <c r="V1" s="14"/>
-      <c r="W1" s="14">
+      <c r="W1" s="14"/>
+      <c r="X1" s="14">
         <v>300</v>
       </c>
-      <c r="X1" s="14"/>
       <c r="Y1" s="14"/>
       <c r="Z1" s="14"/>
       <c r="AA1" s="14"/>
-      <c r="AB1" s="14" t="s">
-        <v>208</v>
-      </c>
+      <c r="AB1" s="14"/>
       <c r="AC1" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="AD1" s="14"/>
+      <c r="AD1" s="14" t="s">
+        <v>208</v>
+      </c>
       <c r="AE1" s="14"/>
       <c r="AF1" s="14"/>
       <c r="AG1" s="14"/>
       <c r="AH1" s="14"/>
       <c r="AI1" s="14"/>
-      <c r="AJ1" s="26" t="s">
+      <c r="AJ1" s="14"/>
+      <c r="AK1" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="AK1" s="14" t="s">
+      <c r="AL1" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="AL1" s="14" t="s">
+      <c r="AM1" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="AM1" s="14"/>
       <c r="AN1" s="14"/>
       <c r="AO1" s="14"/>
       <c r="AP1" s="14"/>
       <c r="AQ1" s="14"/>
       <c r="AR1" s="14"/>
       <c r="AS1" s="14"/>
-      <c r="AU1" s="14"/>
-    </row>
-    <row r="2" spans="1:47" ht="89.25" customHeight="1">
+      <c r="AT1" s="14"/>
+      <c r="AV1" s="14"/>
+    </row>
+    <row r="2" spans="1:48" ht="89.25" customHeight="1">
       <c r="B2" s="7" t="s">
         <v>29</v>
       </c>
@@ -1817,76 +1925,77 @@
       </c>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="42"/>
+      <c r="W2" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="W2" s="19"/>
-      <c r="X2" s="20"/>
-      <c r="Y2" s="18" t="s">
+      <c r="X2" s="19"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" s="19"/>
       <c r="AA2" s="19"/>
-      <c r="AB2" s="3" t="s">
+      <c r="AB2" s="19"/>
+      <c r="AC2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="1" t="s">
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AE2" s="1" t="s">
+      <c r="AF2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AF2" s="1" t="s">
+      <c r="AG2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AG2" s="5" t="s">
+      <c r="AH2" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AH2" s="5" t="s">
+      <c r="AI2" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AI2" s="5" t="s">
+      <c r="AJ2" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AJ2" s="5" t="s">
+      <c r="AK2" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="AK2" s="37" t="s">
+      <c r="AL2" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="AL2" s="10" t="s">
+      <c r="AM2" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AN2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AN2" s="1" t="s">
+      <c r="AO2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="AO2" s="1" t="s">
+      <c r="AP2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AP2" s="1" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AQ2" s="1" t="s">
+      <c r="AR2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AR2" s="1" t="s">
+      <c r="AS2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="AS2" s="1" t="s">
+      <c r="AT2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AT2" s="4" t="s">
+      <c r="AU2" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AU2" s="1" t="s">
+      <c r="AV2" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="31" customHeight="1">
+    <row r="3" spans="1:48" ht="31" customHeight="1">
       <c r="B3" s="8"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1914,36 +2023,38 @@
         <v>70</v>
       </c>
       <c r="V3" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="W3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="X3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="Y3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Z3" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="AA3" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AB3" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AB3" s="2" t="s">
+      <c r="AC3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="AC3" s="2" t="s">
+      <c r="AD3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="AD3" s="2"/>
       <c r="AE3" s="2"/>
       <c r="AF3" s="2"/>
       <c r="AG3" s="2"/>
       <c r="AH3" s="2"/>
-      <c r="AI3" s="9"/>
-      <c r="AJ3" s="2"/>
+      <c r="AI3" s="2"/>
+      <c r="AJ3" s="9"/>
       <c r="AK3" s="2"/>
       <c r="AL3" s="2"/>
       <c r="AM3" s="2"/>
@@ -1951,11 +2062,12 @@
       <c r="AO3" s="2"/>
       <c r="AP3" s="2"/>
       <c r="AQ3" s="2"/>
-      <c r="AR3" s="17"/>
-      <c r="AS3" s="2"/>
-      <c r="AU3" s="2"/>
-    </row>
-    <row r="5" spans="1:47">
+      <c r="AR3" s="2"/>
+      <c r="AS3" s="17"/>
+      <c r="AT3" s="2"/>
+      <c r="AV3" s="2"/>
+    </row>
+    <row r="5" spans="1:48">
       <c r="B5" s="14"/>
       <c r="C5" s="14"/>
       <c r="D5" s="14"/>
@@ -1983,9 +2095,7 @@
       <c r="Z5" s="14"/>
       <c r="AA5" s="14"/>
       <c r="AB5" s="14"/>
-      <c r="AC5" s="14">
-        <v>996</v>
-      </c>
+      <c r="AC5" s="14"/>
       <c r="AD5" s="14"/>
       <c r="AE5" s="14"/>
       <c r="AF5" s="14"/>
@@ -2002,9 +2112,10 @@
       <c r="AQ5" s="14"/>
       <c r="AR5" s="14"/>
       <c r="AS5" s="14"/>
-      <c r="AU5" s="14"/>
-    </row>
-    <row r="6" spans="1:47">
+      <c r="AT5" s="14"/>
+      <c r="AV5" s="14"/>
+    </row>
+    <row r="6" spans="1:48">
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
       <c r="D6" s="14"/>
@@ -2049,9 +2160,10 @@
       <c r="AQ6" s="14"/>
       <c r="AR6" s="14"/>
       <c r="AS6" s="14"/>
-      <c r="AU6" s="14"/>
-    </row>
-    <row r="7" spans="1:47">
+      <c r="AT6" s="14"/>
+      <c r="AV6" s="14"/>
+    </row>
+    <row r="7" spans="1:48">
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
       <c r="D7" s="14"/>
@@ -2096,9 +2208,10 @@
       <c r="AQ7" s="14"/>
       <c r="AR7" s="14"/>
       <c r="AS7" s="14"/>
-      <c r="AU7" s="14"/>
-    </row>
-    <row r="9" spans="1:47">
+      <c r="AT7" s="14"/>
+      <c r="AV7" s="14"/>
+    </row>
+    <row r="9" spans="1:48">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -2110,6 +2223,112 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46AE4196-8FC4-4ED1-B0C4-588DEA137F80}">
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="12.5"/>
+  <sheetData>
+    <row r="1" spans="1:18" ht="124" customHeight="1">
+      <c r="A1" s="45"/>
+      <c r="B1" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1" s="48" t="s">
+        <v>217</v>
+      </c>
+      <c r="I1" s="48" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="K1" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="M1" s="43" t="s">
+        <v>219</v>
+      </c>
+      <c r="N1" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="O1" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="50" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q1" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="R1" s="48" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="46.5">
+      <c r="A2" s="45"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="M2" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="N2" s="49"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:R2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:Q107"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
@@ -3940,7 +4159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:X9"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
@@ -3990,7 +4209,7 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -4209,7 +4428,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B4:O4"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
@@ -4263,7 +4482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A3:I6"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
@@ -4324,7 +4543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:AD6"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
@@ -4483,7 +4702,7 @@
       </c>
       <c r="N4" s="15">
         <f ca="1">DATE(YEAR(TODAY()), MONTH(TODAY()+M4), DAY(TODAY()))</f>
-        <v>46068</v>
+        <v>46136</v>
       </c>
       <c r="O4" s="14"/>
       <c r="P4" s="14"/>
@@ -4524,14 +4743,14 @@
       <c r="K5" s="14"/>
       <c r="L5" s="15">
         <f ca="1">TODAY()</f>
-        <v>46037</v>
+        <v>46105</v>
       </c>
       <c r="M5" s="14">
         <v>21</v>
       </c>
       <c r="N5" s="15">
         <f ca="1">DATE(YEAR(L5),MONTH(L5)+M5,DAY(L5))</f>
-        <v>46675</v>
+        <v>46745</v>
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14"/>
